--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N117_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N117_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.88156553859078</v>
+        <v>8.268254400021004</v>
       </c>
       <c r="D2" t="n">
-        <v>49.19353177790171</v>
+        <v>7.993948913909028</v>
       </c>
       <c r="E2" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F2" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.16369551588058</v>
+        <v>8.964100521330595</v>
       </c>
       <c r="D3" t="n">
-        <v>42.6972499556248</v>
+        <v>6.93830311778903</v>
       </c>
       <c r="E3" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F3" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.030452983376</v>
+        <v>8.9424486097986</v>
       </c>
       <c r="D4" t="n">
-        <v>37.33630940518894</v>
+        <v>6.067150278343203</v>
       </c>
       <c r="E4" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F4" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.2415976047733</v>
+        <v>8.001759610775661</v>
       </c>
       <c r="D5" t="n">
-        <v>33.7963297698116</v>
+        <v>5.491903587594385</v>
       </c>
       <c r="E5" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F5" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.42034492346921</v>
+        <v>5.430806050063747</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48661863735364</v>
+        <v>5.279075528569967</v>
       </c>
       <c r="E6" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F6" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.3502829033079</v>
+        <v>3.469420971787534</v>
       </c>
       <c r="D7" t="n">
-        <v>20.75853666487761</v>
+        <v>3.373262208042611</v>
       </c>
       <c r="E7" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F7" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.17567779145868</v>
+        <v>7.178547641112036</v>
       </c>
       <c r="D8" t="n">
-        <v>23.71654464284201</v>
+        <v>3.853938504461826</v>
       </c>
       <c r="E8" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F8" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.69537548778064</v>
+        <v>5.475498516764355</v>
       </c>
       <c r="D9" t="n">
-        <v>29.01723625709382</v>
+        <v>4.715300891777745</v>
       </c>
       <c r="E9" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F9" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.73385576722536</v>
+        <v>5.319251562174121</v>
       </c>
       <c r="D10" t="n">
-        <v>34.12517659017398</v>
+        <v>5.545341195903272</v>
       </c>
       <c r="E10" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F10" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.96973333500206</v>
+        <v>5.032581666937835</v>
       </c>
       <c r="D11" t="n">
-        <v>13.67447945494779</v>
+        <v>2.222102911429016</v>
       </c>
       <c r="E11" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F11" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.30137411497969</v>
+        <v>6.548973293684201</v>
       </c>
       <c r="D12" t="n">
-        <v>33.09456148674582</v>
+        <v>5.377866241596196</v>
       </c>
       <c r="E12" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F12" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.24191436593922</v>
+        <v>5.401811084465123</v>
       </c>
       <c r="D13" t="n">
-        <v>31.40126712118509</v>
+        <v>5.102705907192577</v>
       </c>
       <c r="E13" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F13" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>45.63410649921587</v>
+        <v>7.415542306122579</v>
       </c>
       <c r="D14" t="n">
-        <v>44.29072161158159</v>
+        <v>7.197242261882009</v>
       </c>
       <c r="E14" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F14" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.54846805448985</v>
+        <v>6.264126058854601</v>
       </c>
       <c r="D15" t="n">
-        <v>47.17532977327966</v>
+        <v>7.665991088157946</v>
       </c>
       <c r="E15" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F15" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>10.45587387256248</v>
+        <v>1.699079504291404</v>
       </c>
       <c r="D16" t="n">
-        <v>49.80237005504996</v>
+        <v>8.092885133945618</v>
       </c>
       <c r="E16" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F16" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>40.12301545764398</v>
+        <v>6.519990011867147</v>
       </c>
       <c r="D17" t="n">
-        <v>17.73950656963401</v>
+        <v>2.882669817565526</v>
       </c>
       <c r="E17" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F17" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>9.621760982420327</v>
+        <v>1.563536159643303</v>
       </c>
       <c r="D18" t="n">
-        <v>62.89743927778851</v>
+        <v>10.22083388264063</v>
       </c>
       <c r="E18" t="n">
-        <v>13.1440198823868</v>
+        <v>2.135903230887854</v>
       </c>
       <c r="F18" t="n">
-        <v>12.45670562588376</v>
+        <v>2.02421466420611</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
